--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5191A635-3D4C-43B8-BDD7-137CDBDFAF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BC7E29-A10A-4DAA-8B56-508EB05EA090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -365,13 +365,24 @@
   </si>
   <si>
     <t>t97</t>
+  </si>
+  <si>
+    <t>双倍加分获取-次数获取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间累计登录可获得1次双倍加分次数</t>
+  </si>
+  <si>
+    <t>1.活动时间内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +414,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -418,12 +435,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -432,7 +464,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -441,6 +473,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,7 +801,9 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -777,37 +820,46 @@
       <c r="I1" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69D7449-899E-4929-90EA-40D56FD0972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841502F8-2092-4426-B096-A395F3E7ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="176">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -698,6 +698,153 @@
     <t>1.登录任务完成
 2.任务状态按钮显示“领取”
 3.按钮颜色高亮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间累计完成任务重复完成奖励重复领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">累计任务已经完成并领取一次
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间累计完成胜利6场匹配/排位模式战斗
+2.已经领取过一次累计任务奖励
+3.再次点击“领取”按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.累计任务按钮显示为“已领取”
+2.不重复发放？
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定任务活动能否重复完成领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动开始前开了一局匹配/排位，活动开始后获得胜利是否算累计任务完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动开启2025年1月15日23：55：00前开启一场匹配/排位模式对局
+2.活动开启后2025年1月16日00：15：00完成对局并胜利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.以结算时间判定？在活动期间内就算累计任务完成累计任务+1
+2.不算任务完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.累计任务进度+1
+2.累计任务进度无反应
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定如何判定累计任务开启前后对局如何作数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在匹配/排位模式期间队友中途退出/断网，对局胜利算不算完成累计任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间进行匹配/排位模式对局
+2.对局期间有队友退出/断网</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进入对局后有队友退出
+2.对局胜利
+3.去活动页面查看累计任务进度是否增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.累计任务完成进度+1
+2.累计任务完成进度不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果累计任务无法增加，会不会让玩家游戏体验很差</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击领取任务奖励瞬间匹配成功，任务奖励发放</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间完成任务之一
+2.点击开始匹配后进入活动页面
+3.点击领取瞬间匹配成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.胜利任务达成
+3.正在匹配中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.以服务器判定为准
+2.正常发放奖励
+3.不正常发放奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定服务器会判定领取奖励是否成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对局平局/失败不会增加累计任务进度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.进行一场匹配/排位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进行一场对局
+2.获得平局/失败
+3.查看活动页面累计活动进度是否增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计任务进度不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动每日首次登录会有红点提示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内首次登录游戏
+2.查看活动页面是否有红点提示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内首次登录游戏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红点提示正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如有可领取奖励，会有红点提示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内完成任务后还未领取奖励</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -766,7 +913,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -776,31 +923,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBEBEBE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBEBEBE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBEBEBE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBEBEBE"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,43 +946,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1167,80 +1299,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B8F594A-F853-48BE-92CE-2E0F7C4D82E4}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.44140625" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" customWidth="1"/>
-    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1252,20 +1385,20 @@
       <c r="G4" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -1277,20 +1410,20 @@
       <c r="G5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="11" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="7" t="s">
         <v>83</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1302,22 +1435,22 @@
       <c r="G6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="H6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -1326,25 +1459,25 @@
       <c r="F7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -1353,25 +1486,25 @@
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="H8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -1380,25 +1513,25 @@
       <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -1407,25 +1540,25 @@
       <c r="F10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="H10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>81</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -1437,20 +1570,20 @@
       <c r="G11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="H11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="3" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="7" t="s">
         <v>80</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -1462,20 +1595,20 @@
       <c r="G12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="H12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="11" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7" t="s">
         <v>82</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -1487,22 +1620,22 @@
       <c r="G13" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="H13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>90</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -1514,20 +1647,20 @@
       <c r="G14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="H14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1539,18 +1672,18 @@
       <c r="G15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="10"/>
+      <c r="H15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -1562,19 +1695,19 @@
       <c r="G16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E17" s="8" t="s">
@@ -1583,23 +1716,23 @@
       <c r="F17" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="H17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1608,23 +1741,23 @@
       <c r="F18" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -1633,25 +1766,25 @@
       <c r="F19" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="H19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>17</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E20" s="8" t="s">
@@ -1671,12 +1804,12 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -1696,12 +1829,12 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="3">
         <v>19</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="8" t="s">
@@ -1721,14 +1854,14 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>97</v>
       </c>
       <c r="E23" s="8" t="s">
@@ -1748,12 +1881,12 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="3">
         <v>21</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="3" t="s">
         <v>101</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -1776,16 +1909,16 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -1794,7 +1927,7 @@
       <c r="F25" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="9" t="s">
         <v>117</v>
       </c>
       <c r="H25" s="8" t="s">
@@ -1805,12 +1938,12 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E26" s="8" t="s">
@@ -1819,7 +1952,7 @@
       <c r="F26" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="9" t="s">
         <v>118</v>
       </c>
       <c r="H26" s="8" t="s">
@@ -1830,12 +1963,12 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="3">
         <v>27</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E27" s="8" t="s">
@@ -1844,7 +1977,7 @@
       <c r="F27" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="9" t="s">
         <v>118</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -1855,14 +1988,14 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="69" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>28</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="6" t="s">
+      <c r="A28" s="3">
+        <v>28</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -1882,16 +2015,16 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="3">
         <v>29</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E29" s="8" t="s">
@@ -1900,7 +2033,7 @@
       <c r="F29" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="9" t="s">
         <v>120</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -1911,12 +2044,12 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="3">
         <v>30</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -1936,9 +2069,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E31" s="8" t="s">
@@ -1958,12 +2091,12 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" t="s">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -1982,12 +2115,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7" t="s">
+    <row r="33" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>134</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -2006,10 +2139,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" t="s">
+    <row r="34" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3" t="s">
         <v>135</v>
       </c>
       <c r="E34" s="8" t="s">
@@ -2028,10 +2161,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" t="s">
+    <row r="35" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -2050,10 +2183,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" t="s">
+    <row r="36" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3" t="s">
         <v>129</v>
       </c>
       <c r="E36" s="8" t="s">
@@ -2072,140 +2205,290 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="37" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>32</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="H37" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>33</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="6" t="s">
+      <c r="B41" s="4"/>
+      <c r="C41" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="H41" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>34</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="6" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="H42" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>35</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="6" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H40" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="H43" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>36</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="B46" s="4"/>
+      <c r="H46" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>37</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B47" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C47" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="H47" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>38</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="6" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="H48" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>39</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B49" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C49" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="D49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>40</v>
       </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="6" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="H51" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>41</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="6" t="s">
+      <c r="B52" s="4"/>
+      <c r="C52" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H52" s="8" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A46">
-    <sortCondition ref="A4:A46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A52">
+    <sortCondition ref="A4:A52"/>
   </sortState>
-  <mergeCells count="17">
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B29:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B46"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B52"/>
     <mergeCell ref="B4:B24"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="C17:C19"/>
@@ -2213,13 +2496,15 @@
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="C20:C22"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="C33:C40"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B29:B46"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H46" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H52" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841502F8-2092-4426-B096-A395F3E7ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B78801B-C4F3-4872-B4FB-D57150F5F2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="194">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -845,6 +845,89 @@
   </si>
   <si>
     <t>活动期间内完成任务后还未领取奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进入活动页面
+2.完成任一活动任务并不领取
+3.查看是否有红点提示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内全部领取奖励后红点消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内完成任务后并领取奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内完成活动任务
+2.领取全部奖励
+3.查看红点提示是否消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红点提示正常消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间每日5点刷新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.先清楚前一日的红点
+2.到刷新时间5点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4：59：59查看红点状态
+2.5：00：00查看红点是否刷新
+3.5：00：01查看红点是否存在</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红点刷新且展示正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>红点层级与状态同步</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有多个没领取的奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.查看活动入口红点
+2.逐层查看红点层级
+3.领取其中一个后返回继续查看</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.层级展示正确
+2.领取后其他红点依旧存在
+3.全部领取后所有红点消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>有未领取奖励时，到红点刷新时间后，未领取奖励红点不消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有未领取奖励且每日红点刷新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.完成活动任务后不消除红点
+2.每日红点刷新后查看红点是否消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未领取奖励红点不会因为每日红点刷新而消失</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -913,7 +996,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -936,13 +1019,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -984,6 +1104,15 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1299,7 +1428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B8F594A-F853-48BE-92CE-2E0F7C4D82E4}">
-  <dimension ref="A1:J52"/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -1308,7 +1440,7 @@
     <col min="4" max="4" width="71.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.21875" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.21875" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
@@ -1329,64 +1461,85 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="6" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>30</v>
@@ -1394,15 +1547,15 @@
     </row>
     <row r="5" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="7" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>26</v>
@@ -1419,75 +1572,77 @@
     </row>
     <row r="6" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="7" t="s">
-        <v>83</v>
+      <c r="C6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>28</v>
@@ -1496,79 +1651,77 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
+      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
@@ -1579,15 +1732,15 @@
     </row>
     <row r="12" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>26</v>
@@ -1602,23 +1755,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="7" t="s">
-        <v>82</v>
+      <c r="C13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>28</v>
@@ -1629,42 +1784,38 @@
     </row>
     <row r="14" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>91</v>
@@ -1675,49 +1826,51 @@
       <c r="H15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>28</v>
@@ -1728,21 +1881,21 @@
     </row>
     <row r="18" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>28</v>
@@ -1751,44 +1904,44 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>39</v>
+        <v>91</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>91</v>
@@ -1805,21 +1958,21 @@
     </row>
     <row r="21" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>91</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>28</v>
@@ -1828,107 +1981,107 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="D22" s="3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>28</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>75</v>
-      </c>
+      <c r="C23" s="4"/>
       <c r="D23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>21</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="D24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>114</v>
+        <v>76</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>28</v>
@@ -1939,18 +2092,18 @@
     </row>
     <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>118</v>
@@ -1962,79 +2115,79 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="C27" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="D27" s="3" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>118</v>
+        <v>107</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="69" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>28</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="10" t="s">
-        <v>75</v>
+      <c r="B28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>119</v>
+        <v>111</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>28</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>29</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>28</v>
@@ -2044,22 +2197,19 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>30</v>
-      </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>124</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>28</v>
@@ -2068,20 +2218,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>31</v>
+      </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>28</v>
@@ -2090,23 +2243,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>31</v>
-      </c>
+    <row r="32" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>28</v>
@@ -2117,17 +2269,15 @@
     </row>
     <row r="33" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>140</v>
@@ -2143,19 +2293,19 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>29</v>
@@ -2165,16 +2315,16 @@
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>130</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>27</v>
@@ -2183,42 +2333,45 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="69" x14ac:dyDescent="0.25">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J36" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>104</v>
@@ -2227,65 +2380,52 @@
         <v>29</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>32</v>
+      </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" s="8"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="3" t="s">
-        <v>145</v>
+      <c r="C40" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>28</v>
@@ -2293,11 +2433,11 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>28</v>
@@ -2305,209 +2445,285 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="10" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>35</v>
-      </c>
+    <row r="43" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B43" s="4"/>
-      <c r="C43" s="10" t="s">
-        <v>77</v>
+      <c r="C43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B44" s="4"/>
-      <c r="C44" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C44" s="4"/>
       <c r="D44" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>104</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>36</v>
+      </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="H45" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>36</v>
-      </c>
-      <c r="B46" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="H46" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>37</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B47" s="4"/>
       <c r="C47" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>38</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="10" t="s">
-        <v>20</v>
+        <v>39</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>39</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="I48" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
       <c r="D49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="4"/>
-      <c r="C50" s="10"/>
+    <row r="50" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>40</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="D50" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>40</v>
-      </c>
-      <c r="B51" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="B51" s="15"/>
       <c r="C51" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>41</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="10" t="s">
-        <v>24</v>
+      <c r="I51" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B52" s="15"/>
+      <c r="C52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>28</v>
       </c>
+      <c r="I52" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>189</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A52">
-    <sortCondition ref="A4:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A51">
+    <sortCondition ref="A3:A51"/>
   </sortState>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="B4:B24"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="C33:C40"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="B29:B46"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C39"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B28:B45"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H52" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B78801B-C4F3-4872-B4FB-D57150F5F2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA89B51A-ACFD-46C9-B3AF-677529E42D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="200">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -928,6 +928,32 @@
   </si>
   <si>
     <t>未领取奖励红点不会因为每日红点刷新而消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如有能够多端登录的情况，两方都点击领取怎么判定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.同一账户两端同时登录
+2.同时领取任务奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内两端同时登录同一账号
+2.任务已完成可领取状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅仅发放一次任务奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定能不能多端登录</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1431,7 +1457,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -2482,139 +2508,137 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="3" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>104</v>
       </c>
       <c r="I44" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="J45" s="8" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>36</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="H45" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>37</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>19</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B46" s="4"/>
       <c r="H46" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
+        <v>37</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>38</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="10" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H47" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="H48" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>39</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B49" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C49" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F49" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>176</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>173</v>
       </c>
       <c r="H49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>40</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>105</v>
@@ -2622,23 +2646,23 @@
     </row>
     <row r="51" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>28</v>
@@ -2648,21 +2672,24 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>41</v>
+      </c>
       <c r="B52" s="15"/>
-      <c r="C52" s="14" t="s">
-        <v>75</v>
+      <c r="C52" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>28</v>
@@ -2671,40 +2698,64 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
+    <row r="53" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B53" s="15"/>
+      <c r="C53" s="14" t="s">
+        <v>75</v>
+      </c>
       <c r="D53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G54" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H53" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="H54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>189</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A51">
-    <sortCondition ref="A3:A51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A52">
+    <sortCondition ref="A3:A52"/>
   </sortState>
   <mergeCells count="19">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="B47:B48"/>
     <mergeCell ref="B3:B23"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="C16:C18"/>
@@ -2716,11 +2767,11 @@
     <mergeCell ref="C28:C31"/>
     <mergeCell ref="C32:C39"/>
     <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B45"/>
+    <mergeCell ref="B28:B46"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H54" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA89B51A-ACFD-46C9-B3AF-677529E42D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429132D2-FE7E-461E-B9AD-E693D26F1AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="412">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -701,10 +701,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>活动期间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>活动期间累计完成任务重复完成奖励重复领取</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -954,6 +950,976 @@
   </si>
   <si>
     <t>不确定能不能多端登录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对局前未定段，但在进行一场战斗后成功定段，会不会使用一次加分</t>
+  </si>
+  <si>
+    <t>如果在首胜刷新之前进入对局，刷新后胜利算不算首胜？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时不知道中途升段能不能使用加分次数，需要和策划沟通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.加分次数减少
+2.加分次数不减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在对局前段位小于超凡，但对局胜利后升至超凡，是否正常使用加分卡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录差一分升至超凡的账号
+2.完成任一任务获取加分次数
+3.进行一场排位后定段成功
+4.回到活动界面查看加分次数是否有减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录未定段账号
+2.完成任一任务获取加分次数
+3.进行一场排位后定段成功
+4.回到活动界面查看加分次数是否有减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划沟通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.领取加分次数
+2.在每日首胜刷新前进入对局
+3.取得战斗胜利
+4.回到活动中心查看加分次数是否有使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日首次参加排位胜利后自动使用1次加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录游戏领取加分次数
+2.正常进行一场排位对局并胜利
+3.加分次数自动-1
+4.回到活动页面查看加分次数是否正常使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.已领取加分次数
+3.段位在未定级-超凡内
+4.等级&gt;=10级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日加分次数最多一次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.仅差一场定段的账号
+2.有加分次数
+3.活动期间内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.仅差一分就升超凡
+2.有加分次数
+3.活动期间内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每日首胜刷新前进入对局
+2.有加分次数
+3.战斗胜利
+4.活动期间内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已经获得过一次加分
+2.再次进行一场对局并胜利
+3.回到活动页面查看加分次数变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.段位在未定级-超凡
+3.有2次及以上加分次数
+4.已经使用过一次每日加分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数清空前1s查看加分次数是否被清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数清空时间查看加分次数是否被清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.还有未使用的加分次数
+2.周一凌晨5：00：00在活动界面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.还有未使用的加分次数
+2.周一凌晨4：59：59待在活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每周一凌晨加分次数刷新前登录游戏
+2.在活动页面待到5：00：00
+3.查看加分次数变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每周一凌晨加分次数刷新前登录游戏
+2.在活动页面待到4：59：59
+3.查看加分次数变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户体验</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周一五点清空加分次数而且首胜刷新时间也是五点，那么是否可以调整活动结束时间也是5点？</t>
+  </si>
+  <si>
+    <t>活动结束时间可调整</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将原本在1月18日0：00：00结束调整为1月19日凌晨5：00：00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要与策划确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数清空时间后1S查看加分次数是否保持被清空的状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一凌晨5：00：01在活动界面刷新后查看加分次数是否保持清空状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周一凌晨5：00：01在活动界面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数依旧为0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果队友/自己消极比赛后获得战斗胜利，会不会使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.对局中队友/自己消极比赛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间进行一场匹配/排位对局
+2.对局内队友/自己消极比赛
+3.获得对局胜利
+4.回到活动页面查看加分次数是否减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不确定消极比赛胜利后符不符合使用条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果队友/自己掉线/中断比赛后获得战斗胜利，会不会使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.对局中队友/自己掉线/中断比赛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间进行一场匹配/排位对局
+2.对局内队友/自己掉线/中断比赛
+3.获得对局胜利
+4.回到活动页面查看加分次数是否减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要确认掉线/中断的具体逻辑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在【赛季-每日首胜】界面中查看剩余加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内
+2.还有未使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内进入【赛季-每日首胜】界面
+2.查看剩余次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常显示剩余未使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动的任务是不是在活动期间只能完成一次？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.重复完成累计任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内多次累计获得战斗胜利
+2.回到活动页面查看累计任务是否可以多次领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要与策划确认是否可以多次完成累计任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可多次完成累计任务并领取奖励？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日点赞数19次点赞任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日点赞数20次点赞任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日点赞数21次点赞任务状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.点赞数达到19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.每日主页点赞
+2.每日好友点赞
+3.每日对局结束后点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务未完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.点赞数达到21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.点赞数达到20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成，可领取奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞数清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞次数清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日点赞数清空前1s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日点赞数清空时5：00：00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日点赞数清空后1s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.有点赞数
+3.4：59：59待在点赞活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每日点赞刷新前4：55：00登录游戏
+2.在点赞活动页面待到4：59：59
+3.查看点赞数是否被清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞数未被清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.有点赞数
+3.5：00：00待在点赞活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每日点赞刷新前4：55：00登录游戏
+2.在点赞活动页面待到5：00：00
+3.查看点赞数是否被清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.有点赞数
+3.5：00：01待在点赞活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同渠道点赞是否都算在内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录的排序方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录的时间规范</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录不随每日点赞清空而清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.好友界面点赞
+3.个人主页面点赞
+4.对局结束后点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录界面没有点赞的时默认展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内点赞
+2.点击查看点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内在收获点赞
+2.好友界面点赞
+3.个人主页面点赞
+4.对局结束后点赞
+5.回到活动页面查看点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有点赞渠道是否都能记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内有点赞记录
+2.点赞记录有多个不同时间段的点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内点赞多次
+2.在活动页面查看点赞记录的时间规范</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认时间规范</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认点赞排序方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认那些点赞渠道算点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内没有任何点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看活动页面点赞记录默认显示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认默认显示是什么</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.每日点赞活动刷新5：00：01后
+2.有点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在每日点赞刷新后5：00：01进入活动页面
+2.点击查看点赞记录是否清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞记录没有清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合时间规范（精确到分？精确到秒？）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>升序？
+降序？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单人点赞是否有上限？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.单人多次点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内获得单人多次点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只算做一次？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认单人点赞上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞对象都有谁？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内
+2.收获不同游戏玩家点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在活动期间内获得不同游戏玩家点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好友？对局内好友？对局内敌人？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认点赞对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>徽章礼包正常获得</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内获得20次点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得奖励并已放入背包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>徽章礼包内的奖励是否可以重复获得？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>徽章礼包内的奖励是否可以在背包内堆叠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>徽章礼包在什么位置领取？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果礼包可以重复领取，累计获得多个奖励时，礼包状态是什么？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包满了，奖励怎么处理？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内获得40/60次点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可重复获得奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要与策划确认是否可以重复完成任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内获得多个徽章礼包并使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内使用徽章礼包
+2.查看在背包内如何堆叠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要与策划确认奖励堆叠状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内获得徽章礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内获得徽章礼包
+2.查看在什么位置领取徽章礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认徽章礼包领取位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内获得多个徽章礼包但不领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内获得多个徽章礼包
+2.查看徽章礼包状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认徽章礼包的堆叠状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.背包内徽章礼包奖励已满
+2.再次获得徽章礼包奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内背包内徽章礼包奖励已满
+2.再次获得徽章礼包奖励
+3.查看奖励如何发放</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内完成点赞任务
+2.兑换徽章礼包
+3.查看徽章礼包存放位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内完成多次点赞任务
+2.回到活动页面查看任务是否可以重复完成领取奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发放至邮箱？或其他位置？有其他处理方式？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认溢出奖励处理方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不满足条件的玩家，活动入口是否显示？如果显示的话条件不足是否有提示？</t>
+  </si>
+  <si>
+    <t>1.活动已开启
+2.等级&lt;10级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.登录9级账号
+2.在活动开启后进入活动页面
+3.查看是如何提示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认是否有提示，如有会提示什么？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼容</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>切后台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多系统</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果多端登录同时领奖怎么处理？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.有待领取奖励
+2.多端同时登录并点击领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.多端同时登录同一个账号
+2.同时点击领取奖励按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认是否可以多端登录且会不会重复领取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>礼包是否在活动结束后也可以正常使用？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动结束后仍有徽章礼包未使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动结束后在仓库中找到未使用的礼包
+2.点击使用礼包
+3.查看礼包能否正常使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常使用？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认徽章礼包的时效性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>礼包内奖励获得的概率/权重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内使用礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用大量的徽章礼包
+2.分别记录各个奖励出现的概率/权重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>与配置表配置一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以多端登录？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动结束后不可在领取/兑换礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动结束前完成任务但不领取/兑换礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动结束2025年1月18日00：00：00前完成任务但不领取/兑换礼包
+2.在活动结束后查看任务可领取状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动显示已结束
+2.不可领取/兑换礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认活动结束后确定不可领取/兑换礼包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时在电脑和手机登录同一账号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在电脑上登录同一账号
+2.在手机上登录同一账号
+3.同时点击进入游戏观察能否同时登录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认是否可以多端登录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击领取奖励的瞬间中断连线重连后奖励补发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动期间内且有可领取礼包
+2.随时准备断网</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进入活动界面
+2.点击领取奖励的瞬间断网
+3. 等待5S后重连观察奖励是否到账</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励已正常发放到对应位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认断网后奖励领取的规则</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多端登录数据是否一致？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在电脑上登录同一账号
+2.在手机上登录同一账号
+3.各在某一端修改某些数据，查看双端数据是否一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在活动页面切后台/锁屏后返回活动页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.账号符合活动条件
+2.在活动界面停留3S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.在活动界面停留3S
+2.切后台/锁屏
+3.等待3S后返回活动界面
+4.查看是否还停留在活动界面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停留在活动界面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一账户在多系统上数据是否一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.IOS系统和安卓系统
+2.一个符合条件的账户</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.分别在不同系统登录同一账户
+2.分别观察不同系统下账户的数据清空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱网清空下点击领取奖励的情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间内有可领取奖励
+2.弱网条件下</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进入活动页面并点击待领取奖励
+2.观察弱网情况下奖励是否到账成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励正常到账</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连续点赞是否算作重复点赞？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好友未点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对好友进行连续点赞并观察是否算多次点赞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只算点赞一次，累计只+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞后取消点赞是否算作点赞？点赞记录是否保留？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对同一人点赞并取消</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.对同一个人先点赞，观察点赞记录
+2.再取消对同一人的点赞，观察点赞记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认是否能取消点赞，如能取消点赞记录是否清除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数是否可以多次使用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">拥有&gt;=2次的加分次数
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进行多场排位并胜利
+2.回到活动页面查看加分次数减少情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数只-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未取得每日首胜时不使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进行一场排位失败后返回活动页面查看加分次数是否减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取得首胜时未定段及超凡以上不会使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用两个账号分别进行一场胜利的排位；观察加分次数是否减少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取得首胜但没有加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.一个未定级账号和一个超凡以上账号
+2.活动期间内且有加分次数
+3.获得战斗胜利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动进行中
+2.没有加分次数
+3.战斗胜利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进行排位胜利
+2.查看是否有使用加分次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常加分，没有额外加分，加分次数不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>低配置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>低配情况下活动页面显示与性能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.低配置设备
+2.符合活动条件的账号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进入游戏并进入活动页面
+2.查看活动页面是否正确
+3.检查性能是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>画面配置正常，性能正常</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -961,7 +1927,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1007,6 +1973,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1022,7 +1995,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1082,27 +2055,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1131,6 +2157,15 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1138,6 +2173,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1457,1324 +2519,2676 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="44.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="95.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="44.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="57.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="25"/>
+    </row>
+    <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="6" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="4" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I4" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="5" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="7" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="6" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="7" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="7" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="10" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="8" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="10" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="9" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="10" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="10" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="10" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="11" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I11" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="12" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="7" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I12" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="13" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="7" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E13" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I13" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="14" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F14" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I14" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="15" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H16" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="17" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I17" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="18" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I18" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="19" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="3" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I19" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="20" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E20" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I20" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="21" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="3" t="s">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I21" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="22" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="3" t="s">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F22" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I22" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="23" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I25" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="26" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>29</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>32</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>33</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>34</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>35</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>36</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>37</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>38</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>39</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>40</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>41</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>42</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>43</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>44</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>45</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>47</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>48</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>49</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="16"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>50</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>51</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>52</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>53</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>54</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>55</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>56</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>57</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>58</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>59</v>
+      </c>
+      <c r="B62" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" s="8" t="s">
+      <c r="C62" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>60</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>61</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>62</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H65" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>63</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    </row>
+    <row r="67" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>64</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>65</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>66</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>67</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>68</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>69</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>70</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>71</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>72</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>73</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>74</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>75</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>76</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>77</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>78</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>79</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>80</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>81</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>82</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>83</v>
+      </c>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>84</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="D87" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>85</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>86</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>87</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>88</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>89</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>90</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>91</v>
+      </c>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>92</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>93</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>94</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>25</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="B97" s="15"/>
+      <c r="C97" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>95</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>96</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="B99" s="16"/>
+      <c r="C99" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H99" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="69" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>28</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>29</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>30</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>31</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="69" x14ac:dyDescent="0.25">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>32</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>33</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>34</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>35</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>36</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="H46" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>37</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>38</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>39</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="8" t="s">
+      <c r="I99" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>40</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>41</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B53" s="15"/>
-      <c r="C53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>189</v>
-      </c>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D119" s="7"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A52">
-    <sortCondition ref="A3:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A6">
+    <sortCondition ref="A4:A6"/>
   </sortState>
-  <mergeCells count="19">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B3:B23"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C39"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B46"/>
+  <mergeCells count="29">
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="C74:C81"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="B95:B99"/>
+    <mergeCell ref="C43:C52"/>
+    <mergeCell ref="B62:B86"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B61"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C91:C94"/>
+    <mergeCell ref="B87:B94"/>
+    <mergeCell ref="B4:B26"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C31:C34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H54" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H99" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429132D2-FE7E-461E-B9AD-E693D26F1AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65213ACC-17C6-4587-BEAF-DB2DD82DE3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="417">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1920,6 +1920,28 @@
   </si>
   <si>
     <t>画面配置正常，性能正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分辨率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同分辨率情况下活动显示是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.手机
+2.平板
+3.PC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在不同设备上登录并查看活动页面显示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动页面显示正常</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2123,7 +2145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2160,19 +2182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2183,6 +2193,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2200,6 +2219,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2519,7 +2544,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
@@ -2536,39 +2561,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="25"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
@@ -2595,10 +2620,10 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -2624,8 +2649,8 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="4" t="s">
         <v>67</v>
       </c>
@@ -2649,8 +2674,8 @@
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="4" t="s">
         <v>83</v>
       </c>
@@ -2674,7 +2699,7 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
         <v>53</v>
       </c>
@@ -2701,7 +2726,7 @@
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="7" t="s">
         <v>54</v>
       </c>
@@ -2728,7 +2753,7 @@
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="7" t="s">
         <v>55</v>
       </c>
@@ -2755,7 +2780,7 @@
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="13"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="7" t="s">
         <v>56</v>
       </c>
@@ -2782,8 +2807,8 @@
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25" t="s">
         <v>79</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -2809,8 +2834,8 @@
       <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="4" t="s">
         <v>80</v>
       </c>
@@ -2834,8 +2859,8 @@
       <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="4" t="s">
         <v>82</v>
       </c>
@@ -2859,8 +2884,8 @@
       <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2886,8 +2911,8 @@
       <c r="A15" s="1">
         <v>12</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
@@ -2909,8 +2934,8 @@
       <c r="A16" s="1">
         <v>13</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="1" t="s">
         <v>70</v>
       </c>
@@ -2931,8 +2956,8 @@
       <c r="A17" s="1">
         <v>14</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="25"/>
+      <c r="C17" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2958,8 +2983,8 @@
       <c r="A18" s="1">
         <v>15</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
@@ -2983,8 +3008,8 @@
       <c r="A19" s="1">
         <v>16</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="1" t="s">
         <v>51</v>
       </c>
@@ -3008,8 +3033,8 @@
       <c r="A20" s="1">
         <v>17</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25" t="s">
         <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -3035,8 +3060,8 @@
       <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="1" t="s">
         <v>69</v>
       </c>
@@ -3060,8 +3085,8 @@
       <c r="A22" s="1">
         <v>19</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="1" t="s">
         <v>70</v>
       </c>
@@ -3085,11 +3110,11 @@
       <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="15" t="s">
         <v>334</v>
       </c>
       <c r="E23" s="5" t="s">
@@ -3115,9 +3140,9 @@
       <c r="A24" s="1">
         <v>21</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="14" t="s">
         <v>226</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -3143,8 +3168,8 @@
       <c r="A25" s="1">
         <v>22</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -3170,8 +3195,8 @@
       <c r="A26" s="1">
         <v>23</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="1" t="s">
         <v>101</v>
       </c>
@@ -3198,10 +3223,10 @@
       <c r="A27" s="1">
         <v>24</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="25" t="s">
         <v>74</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -3227,8 +3252,8 @@
       <c r="A28" s="1">
         <v>25</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="1" t="s">
         <v>92</v>
       </c>
@@ -3252,8 +3277,8 @@
       <c r="A29" s="1">
         <v>26</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
       <c r="D29" s="1" t="s">
         <v>93</v>
       </c>
@@ -3277,7 +3302,7 @@
       <c r="A30" s="1">
         <v>27</v>
       </c>
-      <c r="B30" s="13"/>
+      <c r="B30" s="25"/>
       <c r="C30" s="11"/>
       <c r="D30" s="1" t="s">
         <v>12</v>
@@ -3302,10 +3327,10 @@
       <c r="A31" s="1">
         <v>28</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -3331,8 +3356,8 @@
       <c r="A32" s="1">
         <v>29</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
       <c r="D32" s="1" t="s">
         <v>122</v>
       </c>
@@ -3356,8 +3381,8 @@
       <c r="A33" s="1">
         <v>30</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
       <c r="D33" s="1" t="s">
         <v>123</v>
       </c>
@@ -3381,8 +3406,8 @@
       <c r="A34" s="1">
         <v>31</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
       <c r="D34" s="1" t="s">
         <v>141</v>
       </c>
@@ -3406,8 +3431,8 @@
       <c r="A35" s="1">
         <v>32</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13" t="s">
+      <c r="B35" s="25"/>
+      <c r="C35" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3433,8 +3458,8 @@
       <c r="A36" s="1">
         <v>33</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="1" t="s">
         <v>135</v>
       </c>
@@ -3458,8 +3483,8 @@
       <c r="A37" s="1">
         <v>34</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
       <c r="D37" s="1" t="s">
         <v>128</v>
       </c>
@@ -3483,8 +3508,8 @@
       <c r="A38" s="1">
         <v>35</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
       <c r="D38" s="1" t="s">
         <v>129</v>
       </c>
@@ -3508,8 +3533,8 @@
       <c r="A39" s="1">
         <v>36</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
       <c r="D39" s="1" t="s">
         <v>145</v>
       </c>
@@ -3532,12 +3557,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>37</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
       <c r="D40" s="1" t="s">
         <v>155</v>
       </c>
@@ -3564,8 +3589,8 @@
       <c r="A41" s="1">
         <v>38</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
       <c r="D41" s="1" t="s">
         <v>165</v>
       </c>
@@ -3590,9 +3615,9 @@
       <c r="A42" s="1">
         <v>39</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="18" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="14" t="s">
         <v>249</v>
       </c>
       <c r="E42" s="5" t="s">
@@ -3618,8 +3643,8 @@
       <c r="A43" s="1">
         <v>40</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -3645,8 +3670,8 @@
       <c r="A44" s="1">
         <v>41</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="15"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="1" t="s">
         <v>199</v>
       </c>
@@ -3673,8 +3698,8 @@
       <c r="A45" s="1">
         <v>42</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="15"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="1" t="s">
         <v>203</v>
       </c>
@@ -3701,9 +3726,9 @@
       <c r="A46" s="1">
         <v>43</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="17" t="s">
+      <c r="B46" s="25"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="13" t="s">
         <v>200</v>
       </c>
       <c r="E46" s="5" t="s">
@@ -3729,8 +3754,8 @@
       <c r="A47" s="1">
         <v>44</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="15"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="1" t="s">
         <v>212</v>
       </c>
@@ -3754,8 +3779,8 @@
       <c r="A48" s="1">
         <v>45</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="15"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="1" t="s">
         <v>393</v>
       </c>
@@ -3779,8 +3804,8 @@
       <c r="A49" s="1">
         <v>46</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="15"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="18"/>
       <c r="D49" s="1" t="s">
         <v>397</v>
       </c>
@@ -3804,8 +3829,8 @@
       <c r="A50" s="1">
         <v>47</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="15"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="1" t="s">
         <v>400</v>
       </c>
@@ -3829,8 +3854,8 @@
       <c r="A51" s="1">
         <v>48</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="15"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="1" t="s">
         <v>402</v>
       </c>
@@ -3854,8 +3879,8 @@
       <c r="A52" s="1">
         <v>49</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="16"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="17"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="H52" s="5"/>
@@ -3864,8 +3889,8 @@
       <c r="A53" s="1">
         <v>50</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="14" t="s">
+      <c r="B53" s="25"/>
+      <c r="C53" s="16" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -3891,8 +3916,8 @@
       <c r="A54" s="1">
         <v>51</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="15"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="1" t="s">
         <v>220</v>
       </c>
@@ -3916,8 +3941,8 @@
       <c r="A55" s="1">
         <v>52</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="16"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="17"/>
       <c r="D55" s="1" t="s">
         <v>231</v>
       </c>
@@ -3941,7 +3966,7 @@
       <c r="A56" s="1">
         <v>53</v>
       </c>
-      <c r="B56" s="13"/>
+      <c r="B56" s="25"/>
       <c r="C56" s="7" t="s">
         <v>77</v>
       </c>
@@ -3964,12 +3989,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>54</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13" t="s">
+      <c r="B57" s="25"/>
+      <c r="C57" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -3998,8 +4023,8 @@
       <c r="A58" s="1">
         <v>55</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="1" t="s">
         <v>193</v>
       </c>
@@ -4026,8 +4051,8 @@
       <c r="A59" s="1">
         <v>56</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
       <c r="D59" s="1" t="s">
         <v>240</v>
       </c>
@@ -4054,8 +4079,8 @@
       <c r="A60" s="1">
         <v>57</v>
       </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="1" t="s">
         <v>235</v>
       </c>
@@ -4082,8 +4107,8 @@
       <c r="A61" s="1">
         <v>58</v>
       </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
       <c r="D61" s="1" t="s">
         <v>160</v>
       </c>
@@ -4110,10 +4135,10 @@
       <c r="A62" s="1">
         <v>59</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="16" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -4140,8 +4165,8 @@
       <c r="A63" s="1">
         <v>60</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="1" t="s">
         <v>255</v>
       </c>
@@ -4166,8 +4191,8 @@
       <c r="A64" s="1">
         <v>61</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
       <c r="D64" s="1" t="s">
         <v>256</v>
       </c>
@@ -4192,8 +4217,8 @@
       <c r="A65" s="1">
         <v>62</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="16"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="17"/>
       <c r="D65" s="1" t="s">
         <v>303</v>
       </c>
@@ -4220,8 +4245,8 @@
       <c r="A66" s="1">
         <v>63</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="14" t="s">
+      <c r="B66" s="18"/>
+      <c r="C66" s="16" t="s">
         <v>264</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -4247,8 +4272,8 @@
       <c r="A67" s="1">
         <v>64</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
       <c r="D67" s="1" t="s">
         <v>267</v>
       </c>
@@ -4272,8 +4297,8 @@
       <c r="A68" s="1">
         <v>65</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="16"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="17"/>
       <c r="D68" s="1" t="s">
         <v>268</v>
       </c>
@@ -4297,8 +4322,8 @@
       <c r="A69" s="1">
         <v>66</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="14" t="s">
+      <c r="B69" s="18"/>
+      <c r="C69" s="16" t="s">
         <v>265</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -4327,8 +4352,8 @@
       <c r="A70" s="1">
         <v>67</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
       <c r="D70" s="1" t="s">
         <v>276</v>
       </c>
@@ -4355,8 +4380,8 @@
       <c r="A71" s="1">
         <v>68</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
       <c r="D71" s="1" t="s">
         <v>277</v>
       </c>
@@ -4383,8 +4408,8 @@
       <c r="A72" s="1">
         <v>69</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
       <c r="D72" s="1" t="s">
         <v>280</v>
       </c>
@@ -4411,8 +4436,8 @@
       <c r="A73" s="1">
         <v>70</v>
       </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="16"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="17"/>
       <c r="D73" s="1" t="s">
         <v>278</v>
       </c>
@@ -4436,8 +4461,8 @@
       <c r="A74" s="1">
         <v>71</v>
       </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="14" t="s">
+      <c r="B74" s="18"/>
+      <c r="C74" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -4463,8 +4488,8 @@
       <c r="A75" s="1">
         <v>72</v>
       </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
       <c r="D75" s="1" t="s">
         <v>311</v>
       </c>
@@ -4491,8 +4516,8 @@
       <c r="A76" s="1">
         <v>73</v>
       </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
       <c r="D76" s="1" t="s">
         <v>312</v>
       </c>
@@ -4519,8 +4544,8 @@
       <c r="A77" s="1">
         <v>74</v>
       </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
       <c r="D77" s="1" t="s">
         <v>313</v>
       </c>
@@ -4547,8 +4572,8 @@
       <c r="A78" s="1">
         <v>75</v>
       </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
       <c r="D78" s="1" t="s">
         <v>314</v>
       </c>
@@ -4575,8 +4600,8 @@
       <c r="A79" s="1">
         <v>76</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
       <c r="D79" s="1" t="s">
         <v>351</v>
       </c>
@@ -4603,8 +4628,8 @@
       <c r="A80" s="1">
         <v>77</v>
       </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
       <c r="D80" s="1" t="s">
         <v>346</v>
       </c>
@@ -4631,8 +4656,8 @@
       <c r="A81" s="1">
         <v>78</v>
       </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="16"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="17"/>
       <c r="D81" s="1" t="s">
         <v>357</v>
       </c>
@@ -4659,8 +4684,8 @@
       <c r="A82" s="1">
         <v>79</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="14" t="s">
+      <c r="B82" s="18"/>
+      <c r="C82" s="16" t="s">
         <v>75</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -4689,8 +4714,8 @@
       <c r="A83" s="1">
         <v>80</v>
       </c>
-      <c r="B83" s="15"/>
-      <c r="C83" s="15"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
       <c r="D83" s="1" t="s">
         <v>342</v>
       </c>
@@ -4717,8 +4742,8 @@
       <c r="A84" s="1">
         <v>81</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
       <c r="D84" s="1" t="s">
         <v>384</v>
       </c>
@@ -4742,8 +4767,8 @@
       <c r="A85" s="1">
         <v>82</v>
       </c>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
       <c r="D85" s="1" t="s">
         <v>388</v>
       </c>
@@ -4770,8 +4795,8 @@
       <c r="A86" s="1">
         <v>83</v>
       </c>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
       <c r="D86" s="1" t="s">
         <v>298</v>
       </c>
@@ -4798,10 +4823,10 @@
       <c r="A87" s="1">
         <v>84</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="16" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -4827,8 +4852,8 @@
       <c r="A88" s="1">
         <v>85</v>
       </c>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
       <c r="D88" s="1" t="s">
         <v>173</v>
       </c>
@@ -4852,7 +4877,7 @@
       <c r="A89" s="1">
         <v>86</v>
       </c>
-      <c r="B89" s="15"/>
+      <c r="B89" s="18"/>
       <c r="C89" s="7" t="s">
         <v>23</v>
       </c>
@@ -4879,7 +4904,7 @@
       <c r="A90" s="1">
         <v>87</v>
       </c>
-      <c r="B90" s="15"/>
+      <c r="B90" s="18"/>
       <c r="C90" s="7" t="s">
         <v>24</v>
       </c>
@@ -4906,8 +4931,8 @@
       <c r="A91" s="1">
         <v>88</v>
       </c>
-      <c r="B91" s="15"/>
-      <c r="C91" s="14" t="s">
+      <c r="B91" s="18"/>
+      <c r="C91" s="16" t="s">
         <v>75</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -4933,8 +4958,8 @@
       <c r="A92" s="1">
         <v>89</v>
       </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
       <c r="D92" s="1" t="s">
         <v>365</v>
       </c>
@@ -4961,8 +4986,8 @@
       <c r="A93" s="1">
         <v>90</v>
       </c>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
       <c r="D93" s="1" t="s">
         <v>380</v>
       </c>
@@ -4986,8 +5011,8 @@
       <c r="A94" s="1">
         <v>91</v>
       </c>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
       <c r="D94" s="1" t="s">
         <v>189</v>
       </c>
@@ -5011,10 +5036,10 @@
       <c r="A95" s="1">
         <v>92</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="16" t="s">
         <v>339</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -5043,8 +5068,8 @@
       <c r="A96" s="1">
         <v>93</v>
       </c>
-      <c r="B96" s="15"/>
-      <c r="C96" s="16"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="17"/>
       <c r="D96" s="1" t="s">
         <v>370</v>
       </c>
@@ -5068,7 +5093,7 @@
       <c r="A97" s="1">
         <v>94</v>
       </c>
-      <c r="B97" s="15"/>
+      <c r="B97" s="18"/>
       <c r="C97" s="7" t="s">
         <v>340</v>
       </c>
@@ -5095,7 +5120,7 @@
       <c r="A98" s="1">
         <v>95</v>
       </c>
-      <c r="B98" s="15"/>
+      <c r="B98" s="18"/>
       <c r="C98" s="7" t="s">
         <v>407</v>
       </c>
@@ -5118,57 +5143,65 @@
         <v>38</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>96</v>
-      </c>
-      <c r="B99" s="16"/>
-      <c r="C99" s="7" t="s">
-        <v>341</v>
+    <row r="99" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B99" s="18"/>
+      <c r="C99" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>27</v>
       </c>
       <c r="I99" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>96</v>
+      </c>
+      <c r="B100" s="17"/>
+      <c r="C100" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D119" s="7"/>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D120" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A6">
     <sortCondition ref="A4:A6"/>
   </sortState>
   <mergeCells count="29">
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="C74:C81"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="C43:C52"/>
-    <mergeCell ref="B62:B86"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="C69:C73"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B31:B61"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="C57:C61"/>
     <mergeCell ref="C87:C88"/>
     <mergeCell ref="C91:C94"/>
@@ -5182,10 +5215,26 @@
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="C74:C81"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="B95:B100"/>
+    <mergeCell ref="C43:C52"/>
+    <mergeCell ref="B62:B86"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B61"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H99" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H100" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65213ACC-17C6-4587-BEAF-DB2DD82DE3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6888720-7765-45A6-B754-A17FB02E29CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="423">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1942,6 +1942,34 @@
   </si>
   <si>
     <t>活动页面显示正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动第二天首胜刷新前进行战斗，胜利后到活动第二天</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动期间
+2.有&gt;=1加分次数
+3.排位首胜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.活动第一天23：58：59进入排位对局
+2.排位战斗胜利
+3.活动页面查看加分次数减少情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加分次数只减少1次？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需与策划确认按那天来算</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3303,7 +3331,9 @@
         <v>27</v>
       </c>
       <c r="B30" s="25"/>
-      <c r="C30" s="11"/>
+      <c r="C30" s="11" t="s">
+        <v>417</v>
+      </c>
       <c r="D30" s="1" t="s">
         <v>12</v>
       </c>
@@ -3432,7 +3462,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="25"/>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="16" t="s">
         <v>127</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3459,7 +3489,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="1" t="s">
         <v>135</v>
       </c>
@@ -3484,7 +3514,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="1" t="s">
         <v>128</v>
       </c>
@@ -3509,7 +3539,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="1" t="s">
         <v>129</v>
       </c>
@@ -3534,7 +3564,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="1" t="s">
         <v>145</v>
       </c>
@@ -3562,7 +3592,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="1" t="s">
         <v>155</v>
       </c>
@@ -3590,7 +3620,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="1" t="s">
         <v>165</v>
       </c>
@@ -3616,7 +3646,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
+      <c r="C42" s="17"/>
       <c r="D42" s="14" t="s">
         <v>249</v>
       </c>
@@ -3875,15 +3905,33 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>49</v>
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="17"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="H52" s="5"/>
+      <c r="D52" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="53" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6888720-7765-45A6-B754-A17FB02E29CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACA3DE6-5601-483B-9964-9600F82F0C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84DEF25E-17BC-4B84-A63E-DD8C9AF3675D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="426">
   <si>
     <t>无畏契约测试用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1970,6 +1970,19 @@
   </si>
   <si>
     <t>需与策划确认按那天来算</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱网情况下点击领取/兑换奖励是否正常到账？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.弱网条件下
+2.活动期间内有未领取/兑换奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击领取/兑换查看奖励是否到账</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2572,7 +2585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
@@ -4843,81 +4856,81 @@
       <c r="A86" s="1">
         <v>83</v>
       </c>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
       <c r="D86" s="1" t="s">
-        <v>298</v>
+        <v>423</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>300</v>
+        <v>424</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>301</v>
+        <v>383</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>302</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>84</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>22</v>
-      </c>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
       <c r="D87" s="1" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>170</v>
+        <v>299</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>172</v>
+        <v>301</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I87" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>85</v>
       </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
+      <c r="B88" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="D88" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>172</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I88" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4926,23 +4939,21 @@
         <v>86</v>
       </c>
       <c r="B89" s="18"/>
-      <c r="C89" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="C89" s="18"/>
       <c r="D89" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>105</v>
@@ -4954,19 +4965,19 @@
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>28</v>
@@ -4980,20 +4991,20 @@
         <v>88</v>
       </c>
       <c r="B91" s="18"/>
-      <c r="C91" s="16" t="s">
-        <v>75</v>
+      <c r="C91" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>181</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>28</v>
@@ -5007,134 +5018,136 @@
         <v>89</v>
       </c>
       <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
+      <c r="C92" s="16" t="s">
+        <v>75</v>
+      </c>
       <c r="D92" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>366</v>
+        <v>184</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>367</v>
+        <v>186</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>368</v>
+        <v>187</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>90</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
       <c r="D93" s="1" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>91</v>
       </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
       <c r="D94" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>190</v>
+        <v>380</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>192</v>
+        <v>382</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>92</v>
       </c>
-      <c r="B95" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>339</v>
-      </c>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
       <c r="D95" s="1" t="s">
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>363</v>
+        <v>191</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>93</v>
       </c>
-      <c r="B96" s="18"/>
-      <c r="C96" s="17"/>
+      <c r="B96" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>339</v>
+      </c>
       <c r="D96" s="1" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>362</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>372</v>
+        <v>229</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
@@ -5142,47 +5155,45 @@
         <v>94</v>
       </c>
       <c r="B97" s="18"/>
-      <c r="C97" s="7" t="s">
-        <v>340</v>
-      </c>
+      <c r="C97" s="17"/>
       <c r="D97" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>27</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>95</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="7" t="s">
-        <v>407</v>
+        <v>340</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>27</v>
@@ -5192,21 +5203,24 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>96</v>
+      </c>
       <c r="B99" s="18"/>
-      <c r="C99" s="12" t="s">
-        <v>412</v>
+      <c r="C99" s="7" t="s">
+        <v>407</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>27</v>
@@ -5215,35 +5229,62 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>96</v>
-      </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="7" t="s">
-        <v>341</v>
+        <v>97</v>
+      </c>
+      <c r="B100" s="18"/>
+      <c r="C100" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>27</v>
       </c>
       <c r="I100" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>98</v>
+      </c>
+      <c r="B101" s="17"/>
+      <c r="C101" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D120" s="7"/>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D121" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A6">
@@ -5251,9 +5292,9 @@
   </sortState>
   <mergeCells count="29">
     <mergeCell ref="C57:C61"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C91:C94"/>
-    <mergeCell ref="B87:B94"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C92:C95"/>
+    <mergeCell ref="B88:B95"/>
     <mergeCell ref="B4:B26"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="C17:C19"/>
@@ -5264,16 +5305,16 @@
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C31:C34"/>
     <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="C96:C97"/>
     <mergeCell ref="C74:C81"/>
     <mergeCell ref="A1:J2"/>
-    <mergeCell ref="B95:B100"/>
+    <mergeCell ref="B96:B101"/>
     <mergeCell ref="C43:C52"/>
-    <mergeCell ref="B62:B86"/>
+    <mergeCell ref="B62:B87"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="C66:C68"/>
     <mergeCell ref="C69:C73"/>
-    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="C82:C87"/>
     <mergeCell ref="C35:C42"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B31:B61"/>
@@ -5282,7 +5323,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H100" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H101" xr:uid="{6E28F838-A164-49A4-B9CE-A3793690D3ED}">
       <formula1>"Pass,Fail,NA"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I1048576" xr:uid="{3BCFD62E-BD5F-4F3B-B0EA-A54288EBC456}">
